--- a/docs/tampermonkey/发票模板/良逊清关发票模板.xlsx
+++ b/docs/tampermonkey/发票模板/良逊清关发票模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\代码\hth123321\docs\tampermonkey\发票模板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C445A95-3640-4594-A5AE-8B62BBA1D626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F3FF83-858D-4985-A0FA-E01543F24C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -242,10 +242,6 @@
     </r>
   </si>
   <si>
-    <t>MH15美西卡派专线海运包税</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>带磁</t>
     </r>
@@ -941,6 +937,10 @@
   </si>
   <si>
     <t>{{rawShipment.amazonReferenceId}}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{rawShipment.shipmentName.split('-').pop()}}</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1457,12 +1457,12 @@
         <v>22</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
       <c r="E2" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>20</v>
@@ -1470,7 +1470,7 @@
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
       <c r="I2" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J2" s="12"/>
       <c r="K2" s="12"/>
@@ -1479,15 +1479,15 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>26</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>27</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
       <c r="E3" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>20</v>
@@ -1495,7 +1495,7 @@
       <c r="G3" s="12"/>
       <c r="H3" s="12"/>
       <c r="I3" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J3" s="12"/>
       <c r="K3" s="12"/>
@@ -1504,15 +1504,15 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>30</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>31</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="12"/>
       <c r="E4" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>20</v>
@@ -1520,7 +1520,7 @@
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
       <c r="I4" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J4" s="12"/>
       <c r="K4" s="12"/>
@@ -1529,15 +1529,15 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
       <c r="E5" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>20</v>
@@ -1545,7 +1545,7 @@
       <c r="G5" s="12"/>
       <c r="H5" s="12"/>
       <c r="I5" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J5" s="12"/>
       <c r="K5" s="12"/>
@@ -1554,7 +1554,7 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>16</v>
@@ -1562,15 +1562,15 @@
       <c r="C6" s="12"/>
       <c r="D6" s="12"/>
       <c r="E6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="13" t="s">
         <v>38</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>39</v>
       </c>
       <c r="G6" s="13"/>
       <c r="H6" s="13"/>
       <c r="I6" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J6" s="12"/>
       <c r="K6" s="12"/>
@@ -1579,19 +1579,19 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="12"/>
       <c r="D7" s="12"/>
       <c r="E7" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F7" s="13"/>
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
       <c r="I7" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J7" s="12"/>
       <c r="K7" s="12"/>
@@ -1600,21 +1600,21 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B8" s="12"/>
       <c r="C8" s="12"/>
       <c r="D8" s="12"/>
       <c r="E8" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="13" t="s">
         <v>45</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>46</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
       <c r="I8" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J8" s="12"/>
       <c r="K8" s="12"/>
@@ -1623,7 +1623,7 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>12</v>
@@ -1631,13 +1631,13 @@
       <c r="C9" s="12"/>
       <c r="D9" s="12"/>
       <c r="E9" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F9" s="13"/>
       <c r="G9" s="13"/>
       <c r="H9" s="13"/>
       <c r="I9" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J9" s="12"/>
       <c r="K9" s="12"/>
@@ -1646,7 +1646,7 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>13</v>
@@ -1654,13 +1654,13 @@
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
       <c r="E10" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
       <c r="I10" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J10" s="12"/>
       <c r="K10" s="12"/>
@@ -1669,7 +1669,7 @@
     </row>
     <row r="11" spans="1:15" ht="28.5">
       <c r="A11" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>14</v>
@@ -1677,13 +1677,13 @@
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
       <c r="E11" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F11" s="13"/>
       <c r="G11" s="13"/>
       <c r="H11" s="13"/>
       <c r="I11" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
@@ -1692,7 +1692,7 @@
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>15</v>
@@ -1700,13 +1700,13 @@
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
       <c r="E12" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F12" s="12"/>
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
       <c r="I12" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
@@ -1714,7 +1714,7 @@
     </row>
     <row r="13" spans="1:15" ht="28.5">
       <c r="A13" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B13" s="12">
         <v>1234567890</v>
@@ -1722,13 +1722,13 @@
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
       <c r="E13" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
       <c r="I13" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J13" s="12"/>
       <c r="K13" s="12"/>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
       <c r="E14" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F14" s="12"/>
       <c r="G14" s="12"/>
@@ -1754,15 +1754,15 @@
     </row>
     <row r="15" spans="1:15" ht="28.5">
       <c r="A15" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
       <c r="E15" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="12"/>
@@ -1774,18 +1774,18 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
       <c r="E16" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F16" s="12" t="s">
         <v>68</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>69</v>
       </c>
       <c r="G16" s="12"/>
       <c r="H16" s="12"/>
@@ -1796,67 +1796,67 @@
     </row>
     <row r="17" spans="1:21">
       <c r="A17" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="C17" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="D17" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="E17" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="F17" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="G17" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="H17" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="I17" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="I17" s="8" t="s">
+      <c r="J17" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="J17" s="8" t="s">
+      <c r="K17" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="K17" s="8" t="s">
+      <c r="L17" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="L17" s="8" t="s">
+      <c r="M17" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="M17" s="8" t="s">
+      <c r="N17" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="N17" s="8" t="s">
+      <c r="O17" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="O17" s="8" t="s">
+      <c r="P17" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="P17" s="8" t="s">
+      <c r="Q17" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="Q17" s="8" t="s">
+      <c r="R17" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="R17" s="8" t="s">
+      <c r="S17" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="S17" s="8" t="s">
+      <c r="T17" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="T17" s="8" t="s">
+      <c r="U17" s="8" t="s">
         <v>89</v>
-      </c>
-      <c r="U17" s="8" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:21" s="3" customFormat="1" ht="51" customHeight="1">
@@ -1892,13 +1892,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>6</v>
@@ -1925,10 +1925,10 @@
         <v>17</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P19" s="2"/>
       <c r="Q19" s="11" t="s">
@@ -1966,17 +1966,17 @@
     </row>
     <row r="21" spans="1:21" ht="26.25" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:21" ht="26.25" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:21" ht="26.25" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:21" ht="26.25" customHeight="1"/>
@@ -1989,24 +1989,21 @@
     <row r="31" spans="1:21" ht="26.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="J1:L1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="J12:L12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="J13:L13"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="F11:H11"/>
     <mergeCell ref="J11:L11"/>
@@ -2022,21 +2019,24 @@
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="J10:L10"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="J12:L12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="J13:L13"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="J4:L4"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="3">
